--- a/DateBase/orders/Nhat 48_2026-10-6.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-6.xlsx
@@ -1052,6 +1052,9 @@
       <c r="G2" t="str">
         <v>010101515615102548201515103012957255571221020109101121015101055101055105515551051061010101061030553101010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
